--- a/docs/AIスキル診断_事前アンケート.xlsx
+++ b/docs/AIスキル診断_事前アンケート.xlsx
@@ -1046,7 +1046,7 @@
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ファイル名を「AI診断_御社名_お名前.xlsx」に変更のうえ、事務局までご返送ください。</t>
+          <t>ファイル名を「AI診断_御社名_お名前.xlsx」に変更のうえ、講師までご返送ください。</t>
         </is>
       </c>
     </row>

--- a/docs/AIスキル診断_事前アンケート.xlsx
+++ b/docs/AIスキル診断_事前アンケート.xlsx
@@ -1210,7 +1210,7 @@
       <c r="C11" s="8" t="inlineStr"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>例：yamada@sakura-ss.co.jp</t>
+          <t>例：yamada@example.com</t>
         </is>
       </c>
     </row>
